--- a/public/365_right.xlsx
+++ b/public/365_right.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hohi1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD80C398-9BF7-4847-8868-2842C5CF1334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63071B6E-62C0-4CC8-8BD5-3C5221CA46FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEA7C4ED-1DCF-4007-9303-E1EF37CD0EF8}"/>
+    <workbookView xWindow="4425" yWindow="1215" windowWidth="21600" windowHeight="11295" xr2:uid="{BEA7C4ED-1DCF-4007-9303-E1EF37CD0EF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="175">
   <si>
     <t>[[[126.849174,37.527681],[126.851448,37.527996],[126.863538,37.5262],[126.853433,37.52477],[126.85103,37.524182],[126.849174,37.527681]]]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -327,6 +327,352 @@
   </si>
   <si>
     <t>[[[126.863677,37.539304],[126.858056,37.540478],[126.855159,37.539338],[126.853357,37.537806],[126.853057,37.536172],[126.852713,37.535168],[126.852992,37.534366],[126.853872,37.534468],[126.853872,37.533158],[126.853507,37.532034],[126.854151,37.528766],[126.864042,37.52977],[126.863355,37.536086],[126.863677,37.539304]]]</t>
+  </si>
+  <si>
+    <t>래미안목동아델리체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.851106,37.522057],[126.85249,37.521061],[126.854099,37.517496],[126.850548,37.516568],[126.849786,37.51833],[126.850634,37.518747],[126.850784,37.519359],[126.850494,37.521521],[126.851106,37.522057]]]</t>
+  </si>
+  <si>
+    <t>호반써밋목동아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.848584,37.516015],[126.848874,37.515351],[126.851009,37.515555],[126.853884,37.515964],[126.85456,37.515402],[126.855043,37.515615],[126.854088,37.517513],[126.848584,37.516015]]]</t>
+  </si>
+  <si>
+    <t>신목동아파트2단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.85515,37.515275],[126.854335,37.514662],[126.853895,37.514585],[126.851149,37.513019],[126.850237,37.512653],[126.850129,37.511709],[126.855859,37.513692],[126.85515,37.515275]]]</t>
+  </si>
+  <si>
+    <t>대성유니드아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.846771,37.522143],[126.848681,37.520713],[126.848445,37.516295],[126.848617,37.516031],[126.850526,37.516584],[126.849818,37.518321],[126.850634,37.518764],[126.850773,37.519359],[126.850494,37.52153],[126.851106,37.52205],[126.849861,37.52245],[126.847844,37.522535],[126.846771,37.522143]]]</t>
+  </si>
+  <si>
+    <t>신정뉴타운롯데캐슬아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.847941,37.521241],[126.847157,37.520688],[126.84705,37.519845],[126.845634,37.518023],[126.84852,37.516993],[126.848681,37.520696],[126.847941,37.521241]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신정뉴타운두산위브아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.846782,37.522143],[126.844465,37.520066],[126.845634,37.517997],[126.847029,37.519862],[126.847157,37.520696],[126.847951,37.521258],[126.846782,37.522143]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울신남초등학교, 목동센트럴 1,2단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.845602,37.518031],[126.844711,37.517035],[126.842179,37.51615],[126.840323,37.515494],[126.840806,37.514404],[126.84307,37.515077],[126.843199,37.514838],[126.844336,37.515085],[126.844711,37.515562],[126.846085,37.51552],[126.848863,37.515332],[126.848434,37.51632],[126.84852,37.517044],[126.845602,37.518031]]]</t>
+  </si>
+  <si>
+    <t>목동센트럴 1,4단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.840345,37.515511],[126.839647,37.517112],[126.841257,37.517674],[126.842222,37.518346],[126.844422,37.520032],[126.845623,37.518023],[126.844722,37.517018],[126.840345,37.515511]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계남 제 1근린공원, 신정이편한세상아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.840742,37.514405],[126.842952,37.509229],[126.850097,37.511723],[126.850237,37.512728],[126.853917,37.514625],[126.854303,37.514727],[126.85514,37.515358],[126.855097,37.515681],[126.854539,37.515409],[126.853917,37.515988],[126.84881,37.515306],[126.84484,37.515596],[126.844475,37.515136],[126.843209,37.51483],[126.843059,37.515153],[126.840742,37.514405]]]</t>
+  </si>
+  <si>
+    <t>남부순환로 75길</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.837695,37.520958],[126.839508,37.517051],[126.841289,37.517689],[126.844465,37.520073],[126.843048,37.522278],[126.837695,37.520958]]]</t>
+  </si>
+  <si>
+    <t>잠수공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.843016,37.522286],[126.85087,37.524074],[126.852565,37.521103],[126.851084,37.522107],[126.849926,37.522474],[126.847941,37.52261],[126.846825,37.522218],[126.844454,37.520107],[126.843016,37.522286]]]</t>
+  </si>
+  <si>
+    <t>서울양강초, 양강중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.840699,37.526347],[126.843016,37.522329],[126.850848,37.524083],[126.848981,37.527777],[126.840699,37.526347]]]</t>
+  </si>
+  <si>
+    <t>서울강서초등학교, 삼익플라주행복한마을아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.840688,37.526338],[126.83497,37.525487],[126.837695,37.520984],[126.843016,37.522303],[126.840688,37.526338]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸른마을3단지 아파트, 강신중, 근린공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.839497,37.51706],[126.833349,37.515221],[126.835699,37.511943],[126.83645,37.510504],[126.841632,37.512258],[126.839497,37.51706]]]</t>
+  </si>
+  <si>
+    <t>동일하이빌2단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.836472,37.510499],[126.838253,37.507076],[126.840892,37.508507],[126.842898,37.509145],[126.841611,37.512261],[126.836472,37.510499]]]</t>
+  </si>
+  <si>
+    <t>신월시영아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.839454,37.517127],[126.833704,37.515424],[126.83321,37.516395],[126.831686,37.517127],[126.831193,37.517604],[126.831129,37.518898],[126.831772,37.520226],[126.833532,37.52232],[126.835806,37.523734],[126.839454,37.517127]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신정이펜하우스 1,2단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.833768,37.515391],[126.828682,37.514029],[126.819069,37.513007],[126.819799,37.514131],[126.828125,37.521248],[126.828275,37.522797],[126.830506,37.521623],[126.830614,37.520805],[126.831729,37.520209],[126.83115,37.519],[126.831129,37.517672],[126.831772,37.517042],[126.833317,37.516361],[126.833768,37.515391]]]</t>
+  </si>
+  <si>
+    <t>신안파크아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.828189,37.522899],[126.830549,37.521657],[126.830635,37.520822],[126.831772,37.520192],[126.83351,37.522304],[126.835935,37.523836],[126.834927,37.525521],[126.82806,37.524483],[126.828189,37.522899]]]</t>
+  </si>
+  <si>
+    <t>신정이펜하우스 3단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.819048,37.512992],[126.816258,37.508565],[126.814907,37.505738],[126.836836,37.506657],[126.838253,37.5071],[126.83645,37.510506],[126.835635,37.512005],[126.83336,37.515223],[126.828661,37.514031],[126.819048,37.512992]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장안사산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.828125,37.524481],[126.815293,37.522523],[126.814413,37.51859],[126.812825,37.512868],[126.819134,37.513038],[126.828125,37.521212],[126.828189,37.522812],[126.828125,37.524481]]]</t>
+  </si>
+  <si>
+    <t>시루뫼 사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.819091,37.513044],[126.812611,37.512822],[126.807117,37.512396],[126.807826,37.510779],[126.808019,37.508207],[126.808448,37.506692],[126.814907,37.505687],[126.819091,37.513044]]]</t>
+  </si>
+  <si>
+    <t>신정현대아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.829133,37.506371],[126.829069,37.502199],[126.844561,37.505894],[126.842973,37.50913],[126.840935,37.508483],[126.83836,37.507138],[126.836922,37.506661],[126.829133,37.506371]]]</t>
+  </si>
+  <si>
+    <t>매몽초, 개봉중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.829112,37.502164],[126.842211,37.499953],[126.84322,37.500395],[126.846535,37.501562],[126.844604,37.505912],[126.829112,37.502164]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신트리 3,4단지, 신정현대아파트 5단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학마을아파트 1,2단지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.844046,37.507035],[126.845462,37.507512],[126.845881,37.50683],[126.848767,37.50781],[126.849947,37.507427],[126.85028,37.508687],[126.848745,37.51119],[126.842984,37.509206],[126.844046,37.507035]]]</t>
+  </si>
+  <si>
+    <t>안일유앤아이아파트, 삼익2차아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.850011,37.507452],[126.851074,37.507596],[126.851803,37.507528],[126.853123,37.506932],[126.854002,37.506702],[126.855397,37.505715],[126.855741,37.505119],[126.860043,37.506753],[126.859839,37.507068],[126.858391,37.506515],[126.855977,37.506694],[126.854614,37.5097],[126.852736,37.509572],[126.850301,37.508703],[126.850011,37.507452]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고척파크푸르지오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.858144,37.509981],[126.854678,37.5097],[126.855966,37.506694],[126.858348,37.506515],[126.859828,37.507094],[126.858144,37.509981]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울세곡초</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.846986,37.50724],[126.849239,37.502642],[126.855773,37.505103],[126.855386,37.505716],[126.854013,37.506747],[126.853112,37.506925],[126.851825,37.507564],[126.851041,37.507632],[126.850044,37.507453],[126.848756,37.507811],[126.846986,37.50724]]]</t>
+  </si>
+  <si>
+    <t>세곡초와 개봉중 사이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.846964,37.507198],[126.845859,37.506823],[126.845495,37.507504],[126.844003,37.507062],[126.846578,37.501561],[126.849207,37.502642],[126.846964,37.507198]]]</t>
+  </si>
+  <si>
+    <t>와룡산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.814799,37.505779],[126.813447,37.500874],[126.814349,37.498302],[126.822524,37.498881],[126.826,37.497076],[126.829176,37.497672],[126.829047,37.506375],[126.814799,37.505779]]]</t>
+  </si>
+  <si>
+    <t>온수힐스테이트아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.814263,37.498318],[126.824005,37.492714],[126.827095,37.493344],[126.827073,37.494145],[126.825292,37.495559],[126.82615,37.496564],[126.826022,37.497092],[126.822546,37.498931],[126.814263,37.498318]]]</t>
+  </si>
+  <si>
+    <t>우신빌라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.829197,37.497682],[126.826054,37.497102],[126.82614,37.496592],[126.825324,37.49557],[126.827073,37.494147],[126.827095,37.493262],[126.831644,37.493228],[126.829197,37.497682]]]</t>
+  </si>
+  <si>
+    <t>동북골든아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.829154,37.502167],[126.829305,37.497722],[126.831708,37.493277],[126.837587,37.493226],[126.841235,37.494946],[126.839476,37.49733],[126.839561,37.498284],[126.84233,37.499987],[126.829154,37.502167]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울오류초등학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.841257,37.494946],[126.846707,37.497347],[126.847179,37.49779],[126.848595,37.498182],[126.846642,37.501554],[126.84248,37.500055],[126.83969,37.498352],[126.839411,37.497347],[126.841257,37.494946]]]</t>
+  </si>
+  <si>
+    <t>개봉푸르지오아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.849968,37.502943],[126.852415,37.497919],[126.850623,37.498293],[126.848874,37.498097],[126.846675,37.501563],[126.849968,37.502943]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경인중, 고척삼명아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.850022,37.502917],[126.852415,37.497927],[126.854088,37.497365],[126.856492,37.497322],[126.857028,37.499613],[126.857318,37.499894],[126.856556,37.500158],[126.855698,37.500218],[126.855676,37.50061],[126.853874,37.501248],[126.852951,37.501469],[126.853294,37.502082],[126.852715,37.502662],[126.853831,37.503121],[126.853659,37.503547],[126.854582,37.50462],[126.850022,37.502917]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고척대우아파트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.860054,37.506767],[126.86162,37.504212],[126.860676,37.503923],[126.857393,37.49992],[126.855698,37.500261],[126.855741,37.500619],[126.852951,37.501487],[126.853273,37.502135],[126.852694,37.502662],[126.853831,37.503139],[126.853638,37.503514],[126.854603,37.504672],[126.860054,37.506767]]]</t>
+  </si>
+  <si>
+    <t>고척산업용품종합상가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.861641,37.504282],[126.865075,37.498083],[126.862886,37.496669],[126.856492,37.497334],[126.857028,37.49965],[126.860611,37.503891],[126.861641,37.504282]]]</t>
+  </si>
+  <si>
+    <t>은데미공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.804776,37.521368],[126.811256,37.521964],[126.815333,37.52256],[126.812822,37.512821],[126.807158,37.512378],[126.804819,37.517861],[126.804776,37.521368]]]</t>
+  </si>
+  <si>
+    <t>곰달래로24길</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.847383,37.530624],[126.844164,37.530428],[126.844336,37.528428],[126.848423,37.528683],[126.847383,37.530624]]]</t>
+  </si>
+  <si>
+    <t>레인보우모텔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.844153,37.530428],[126.83836,37.530037],[126.839529,37.528155],[126.844282,37.528436],[126.844153,37.530428]]]</t>
+  </si>
+  <si>
+    <t>신월중앙시장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.848423,37.528675],[126.839508,37.528164],[126.840688,37.526351],[126.848971,37.527798],[126.848423,37.528675]]]</t>
+  </si>
+  <si>
+    <t>강서교회, 곰달래어린이공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.838349,37.530037],[126.83247,37.529679],[126.834948,37.525534],[126.840742,37.526351],[126.838349,37.530037]]]</t>
+  </si>
+  <si>
+    <t>서서울호수공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.820185,37.534723],[126.821623,37.534944],[126.828253,37.535898],[126.832545,37.529599],[126.835012,37.525513],[126.827953,37.524491],[126.826987,37.529939],[126.820185,37.534723]]]</t>
+  </si>
+  <si>
+    <t>태형사우나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.828339,37.535915],[126.834261,37.536766],[126.838403,37.53011],[126.83248,37.529701],[126.828339,37.535915]]]</t>
+  </si>
+  <si>
+    <t>치유하는교회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.837405,37.531619],[126.839336,37.532402],[126.843896,37.532666],[126.845677,37.5335],[126.847415,37.530657],[126.838413,37.530078],[126.837405,37.531619]]]</t>
+  </si>
+  <si>
+    <t>화원중학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.839315,37.532428],[126.838961,37.532998],[126.840827,37.533679],[126.838714,37.537262],[126.842523,37.538625],[126.845698,37.533535],[126.843853,37.532649],[126.839315,37.532428]]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울월정초등학교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[[126.834197,37.536786],[126.838789,37.537348],[126.84087,37.533671],[126.838961,37.532973],[126.839304,37.532411],[126.837459,37.531645],[126.834197,37.536786]]]</t>
   </si>
 </sst>
 </file>
@@ -729,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3FC816-E7CB-4286-92DF-FFAD7C89E12C}">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T88"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
@@ -1133,6 +1479,390 @@
         <v>79</v>
       </c>
     </row>
+    <row r="41" spans="1:2" ht="17.25">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
